--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.70319615694763</v>
+        <v>3.039269375503989</v>
       </c>
       <c r="D2" t="n">
-        <v>18.23260998432542</v>
+        <v>2.962799122452881</v>
       </c>
       <c r="E2" t="n">
-        <v>3.893494855470215</v>
+        <v>0.6326929140139099</v>
       </c>
       <c r="F2" t="n">
-        <v>3.863199022673563</v>
+        <v>0.6277698411844539</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.58713666576479</v>
+        <v>1.882909708186779</v>
       </c>
       <c r="D3" t="n">
-        <v>11.46593599520324</v>
+        <v>1.863214599220527</v>
       </c>
       <c r="E3" t="n">
-        <v>3.893494855470215</v>
+        <v>0.6326929140139099</v>
       </c>
       <c r="F3" t="n">
-        <v>3.863199022673563</v>
+        <v>0.6277698411844539</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.82422163225641</v>
+        <v>3.546436015241666</v>
       </c>
       <c r="D4" t="n">
-        <v>21.92543559141122</v>
+        <v>3.562883283604322</v>
       </c>
       <c r="E4" t="n">
-        <v>3.893494855470215</v>
+        <v>0.6326929140139099</v>
       </c>
       <c r="F4" t="n">
-        <v>3.863199022673563</v>
+        <v>0.6277698411844539</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.64432056975584</v>
+        <v>2.379702092585324</v>
       </c>
       <c r="D5" t="n">
-        <v>15.07198401275111</v>
+        <v>2.449197402072056</v>
       </c>
       <c r="E5" t="n">
-        <v>3.893494855470215</v>
+        <v>0.6326929140139099</v>
       </c>
       <c r="F5" t="n">
-        <v>3.863199022673563</v>
+        <v>0.6277698411844539</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
